--- a/portfolio_eak.xlsx
+++ b/portfolio_eak.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\StockInvestment\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\StockInvestment\StockInvestment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{662D6FF2-37CE-421A-AA16-33DD493241D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8B2A9CE-0C7E-4936-9FA4-22E691052ACC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4260" yWindow="4635" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -485,9 +485,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -498,18 +498,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B2">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="C2">
-        <v>10.52</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>9.9600000000000009</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -520,7 +520,7 @@
         <v>13.02</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
@@ -531,7 +531,7 @@
         <v>4.6500000000000004</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="b">
         <v>1</v>
       </c>
@@ -542,7 +542,7 @@
         <v>4.83</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>8</v>
       </c>
@@ -553,7 +553,7 @@
         <v>2.94</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>9</v>
       </c>
@@ -564,7 +564,7 @@
         <v>14.52</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
@@ -575,7 +575,7 @@
         <v>11.8</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>11</v>
       </c>
@@ -586,7 +586,7 @@
         <v>16.190000000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>12</v>
       </c>
@@ -597,18 +597,18 @@
         <v>27.32</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B11">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="C11">
-        <v>38.94</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+        <v>26.36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>14</v>
       </c>
@@ -619,7 +619,7 @@
         <v>12.39</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>15</v>
       </c>
@@ -630,7 +630,7 @@
         <v>22.85</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>16</v>
       </c>
@@ -641,7 +641,7 @@
         <v>5.51</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>17</v>
       </c>
@@ -652,7 +652,7 @@
         <v>23.27</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>18</v>
       </c>
@@ -663,7 +663,7 @@
         <v>3.81</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
         <v>19</v>
       </c>
@@ -674,7 +674,7 @@
         <v>2.0699999999999998</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>20</v>
       </c>
@@ -685,7 +685,7 @@
         <v>42.61</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
         <v>21</v>
       </c>
@@ -696,7 +696,7 @@
         <v>24.37</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>22</v>
       </c>
@@ -707,7 +707,7 @@
         <v>23.54</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
         <v>3</v>
       </c>
@@ -718,7 +718,7 @@
         <v>27.8</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>23</v>
       </c>
@@ -729,7 +729,7 @@
         <v>70.489999999999995</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
         <v>24</v>
       </c>
@@ -740,7 +740,7 @@
         <v>43.75</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
         <v>25</v>
       </c>
@@ -751,7 +751,7 @@
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
         <v>26</v>
       </c>
@@ -762,7 +762,7 @@
         <v>20.18</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
         <v>27</v>
       </c>
@@ -773,7 +773,7 @@
         <v>7.64</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
         <v>28</v>
       </c>
@@ -784,7 +784,7 @@
         <v>8.17</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
         <v>4</v>
       </c>
@@ -795,7 +795,7 @@
         <v>53.84</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
         <v>29</v>
       </c>
@@ -806,7 +806,7 @@
         <v>25.42</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
         <v>30</v>
       </c>

--- a/portfolio_eak.xlsx
+++ b/portfolio_eak.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\StockInvestment\StockInvestment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8B2A9CE-0C7E-4936-9FA4-22E691052ACC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5F31941-15F7-4705-9A0C-FFB92AAE0FC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -514,10 +514,10 @@
         <v>6</v>
       </c>
       <c r="B3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="C3">
-        <v>13.02</v>
+        <v>17.329999999999998</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
